--- a/tests/test_data/nota_credito/nota_credito_casos.xlsx
+++ b/tests/test_data/nota_credito/nota_credito_casos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ErickAlejandroRodríg\Desktop\Entorno\Auto FACTO 8\automation_framework\tests\test_data\nota_credito\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCFF418-0DF8-4FD1-89F7-633E4C1EAB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAD480F-B2B9-44FA-BEEF-C22191EDE574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>ejecutar</t>
   </si>
@@ -191,12 +191,6 @@
     <t>NID200929V26 - PRUEBAS - Pruebas</t>
   </si>
   <si>
-    <t>XAXX010101000</t>
-  </si>
-  <si>
-    <t>03104</t>
-  </si>
-  <si>
     <t>616 - Sin obligaciones fiscales</t>
   </si>
   <si>
@@ -251,9 +245,6 @@
     <t>01 - Efectivo</t>
   </si>
   <si>
-    <t xml:space="preserve"> EEEEEEEE-E986-47B0-9969-115075E80965</t>
-  </si>
-  <si>
     <t>Pieza</t>
   </si>
   <si>
@@ -269,7 +260,13 @@
     <t>002 - IVA</t>
   </si>
   <si>
-    <t>CFDI PUBLICO GENERAL</t>
+    <t>EEEEEEEE-A186-4B66-8BE7-29B09A969A5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROEE9706122J0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erick Alejandro Rodriguez Elvira </t>
   </si>
 </sst>
 </file>
@@ -322,7 +319,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,18 +626,21 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="47.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="9" max="9" width="26" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="41.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="17" width="15" customWidth="1"/>
+    <col min="12" max="12" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.6328125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="26.90625" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
     <col min="20" max="20" width="18.90625" bestFit="1" customWidth="1"/>
@@ -829,85 +829,85 @@
         <v>51</v>
       </c>
       <c r="F2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2">
+        <v>56420</v>
+      </c>
+      <c r="I2" t="s">
         <v>52</v>
       </c>
-      <c r="G2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>54</v>
-      </c>
-      <c r="J2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" t="s">
-        <v>56</v>
       </c>
       <c r="R2" s="2">
         <v>46141.465752314813</v>
       </c>
       <c r="S2" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" t="s">
         <v>58</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
+        <v>68</v>
+      </c>
+      <c r="W2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" t="s">
         <v>59</v>
       </c>
-      <c r="U2" t="s">
+      <c r="Y2" t="s">
         <v>60</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="s">
         <v>70</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AD2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG2" t="s">
         <v>71</v>
-      </c>
-      <c r="X2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>74</v>
       </c>
       <c r="AH2">
         <v>50</v>
       </c>
       <c r="AI2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL2" t="s">
         <v>64</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AM2" t="s">
         <v>65</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>67</v>
       </c>
       <c r="AN2">
         <v>16</v>
@@ -919,13 +919,13 @@
         <v>48</v>
       </c>
       <c r="AS2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AU2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AV2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
